--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 05.05.2025 a 11.05.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 05.05.2025 a 11.05.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28906"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CA8E11A-1450-441C-8E11-97D020CBCF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A535DC65-4492-42D4-8BDF-A5E54D716B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="05.05" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="124">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -337,6 +337,96 @@
   </si>
   <si>
     <t>ROSIMEIRE APARECIDA DE SOUZA MENDES 18607238884</t>
+  </si>
+  <si>
+    <t>ELIENE DA SILVA FERREIRA CPF 84654023100</t>
+  </si>
+  <si>
+    <t>A pedido segurado</t>
+  </si>
+  <si>
+    <t>ELAINE MARIA XAVIER  09567754896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicidade 5177202451310982302 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRESSA LIN RAMOS MEDEIROS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTHUR AUGUSTO BORGES OLIVEIRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS AUGUSTO DA SILVA OLIVEIRA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS MARCELO LOPES RIBEIRO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo (Foto cortando as observações). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRISTIAN LUIZ NOGAROTTO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA LUCIA DOS SANTOS FERRUFINO           </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo - não tirou foto do passo solicitado,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANA DE CASSIA ARAUJO DALLMANN              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO SILVA SOUSA                         </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Foto 45º - Frente e Lateral Esquerda- não tirou foto do passo solicitado, Foto 45º - Traseira e Lateral Esquerda-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME ABRAAO ALVES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUE CARDOSO BONALDO                     </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.05.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA KAROLINE DA SILVA PINHEIRO           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA CRISTINA LEDESMA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L P DA SILVA BEZERRA ME                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONI CAMILO DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGIA MARIA TAPIA MACIEL DA CRUZ             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOURDES BUCHI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS RAFAEL FERREIRA BARRETO               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA EDUARDA MIRANDA SALES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NYCOLAS GABRIEL DA SILVA DOS SANTOS          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTA IANNI AIROLDI                        </t>
+  </si>
+  <si>
+    <t>SOARES BARBOSA SOCIEDADE INDIVIDUAL DE ADVOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAIS CAROLINE RAMOS ROCHA                   </t>
   </si>
 </sst>
 </file>
@@ -497,7 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,6 +627,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2946,7 +3045,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2957,7 +3056,7 @@
     <col min="6" max="6" width="52.85546875" customWidth="1"/>
     <col min="7" max="7" width="23.140625" customWidth="1"/>
     <col min="8" max="8" width="32.140625" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2985,7 +3084,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2999,8 +3098,8 @@
       <c r="C2" s="7">
         <v>45784</v>
       </c>
-      <c r="D2" s="8">
-        <v>0</v>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="E2" s="8">
         <v>3449977795</v>
@@ -3019,249 +3118,693 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45812</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3449975672</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
+      <c r="B4" s="7">
+        <v>45782</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
+        <v>3449977135</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
+      <c r="B5" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D5" s="8">
+        <v>132365888</v>
+      </c>
+      <c r="E5" s="8">
+        <v>3449975309</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="20">
+        <v>45777</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45772</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D6" s="8">
+        <v>132293583</v>
+      </c>
+      <c r="E6" s="8">
+        <v>3449970205</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="20">
+        <v>45772</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45784</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D7" s="8">
+        <v>132434735</v>
+      </c>
+      <c r="E7" s="8">
+        <v>3449978917</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="20">
+        <v>45784</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45775</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D8" s="8">
+        <v>132359501</v>
+      </c>
+      <c r="E8" s="8">
+        <v>3449972515</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="20">
+        <v>45775</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D9" s="8">
+        <v>132364489</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3449975090</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="20">
+        <v>45777</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>45779</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D10" s="8">
+        <v>132384015</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3449976409</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="20">
+        <v>45779</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D11" s="8">
+        <v>132365063</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3449975122</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="20">
+        <v>45777</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>45776</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D12" s="8">
+        <v>132362812</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3449973373</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="20">
+        <v>45776</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D13" s="8">
+        <v>132365156</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3449975177</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="20">
+        <v>45777</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D14" s="8">
+        <v>132386295</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3449976596</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="20">
+        <v>45783</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D15" s="8">
+        <v>132364624</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3449975100</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="20">
+        <v>45777</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D16" s="8">
+        <v>132363520</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3449974924</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D17" s="8">
+        <v>132357992</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3449974484</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D18" s="8">
+        <v>132365085</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3449975155</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45784</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D19" s="8">
+        <v>132382561</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3449976310</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="20">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45772</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D20" s="8">
+        <v>132298362</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3449970634</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="20">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45782</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D21" s="8">
+        <v>132424157</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3449977564</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="20">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D22" s="8">
+        <v>132364304</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3449975078</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45771</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D23" s="8">
+        <v>132281203</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3449969490</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="20">
+        <v>45771</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D24" s="8">
+        <v>132361295</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3449974760</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="20">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D25" s="8">
+        <v>132358100</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3449974517</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45777</v>
+      </c>
+      <c r="C26" s="7">
+        <v>45784</v>
+      </c>
+      <c r="D26" s="8">
+        <v>132362352</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3449974825</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="20">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="8"/>
       <c r="C27" s="7"/>
@@ -3271,7 +3814,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="8"/>
       <c r="C28" s="7"/>
@@ -3281,7 +3824,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="8"/>
       <c r="C29" s="7"/>
@@ -3291,7 +3834,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="8"/>
       <c r="C30" s="7"/>
@@ -3301,7 +3844,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="8"/>
       <c r="C31" s="7"/>
@@ -3311,7 +3854,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="8"/>
       <c r="C32" s="7"/>
@@ -3531,47 +4074,17 @@
       <c r="G53" s="6"/>
       <c r="H53" s="9"/>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A6" xr:uid="{14638D70-6DB5-4E9D-A221-CDD8F04EA206}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A26" xr:uid="{14638D70-6DB5-4E9D-A221-CDD8F04EA206}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G12" xr:uid="{742EA6F6-6444-4436-BC8B-14077150C3DC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G26" xr:uid="{742EA6F6-6444-4436-BC8B-14077150C3DC}">
       <formula1>"Duplicidade,Falta de Vistoria,Bônus,Vistoria Recusada,Vistoria Frustrada,Desistência,Demais Motivos,Inadimplêmcia,Policita de Aceitação,"</formula1>
     </dataValidation>
   </dataValidations>
